--- a/outputs/45372.xlsx
+++ b/outputs/45372.xlsx
@@ -123,20 +123,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -144,7 +148,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -400,188 +404,185 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <f aca="false">IF(IF(A2&lt;TIME(9,45,0),B2,C2)=0,"",IF(A2&lt;TIME(9,45,0),B2,C2))</f>
+      <c r="E2" s="5" t="n">
+        <f aca="false">IF(IF(A2&lt;0.40625,B2,C2)=0,"",IF(A2&lt;0.40625,B2,C2))</f>
         <v>42</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>0.34375</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <f aca="false">IF(IF(A3&lt;TIME(9,45,0),B3,C3)=0,"",IF(A3&lt;TIME(9,45,0),B3,C3))</f>
+      <c r="E3" s="5" t="n">
+        <f aca="false">IF(IF(A3&lt;0.40625,B3,C3)=0,"",IF(A3&lt;0.40625,B3,C3))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>0.354166666666667</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <f aca="false">IF(IF(A4&lt;TIME(9,45,0),B4,C4)=0,"",IF(A4&lt;TIME(9,45,0),B4,C4))</f>
+      <c r="E4" s="5" t="n">
+        <f aca="false">IF(IF(A4&lt;0.40625,B4,C4)=0,"",IF(A4&lt;0.40625,B4,C4))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>0.364583333333333</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <f aca="false">IF(IF(A5&lt;TIME(9,45,0),B5,C5)=0,"",IF(A5&lt;TIME(9,45,0),B5,C5))</f>
+      <c r="E5" s="5" t="n">
+        <f aca="false">IF(IF(A5&lt;0.40625,B5,C5)=0,"",IF(A5&lt;0.40625,B5,C5))</f>
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>0.375</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <f aca="false">IF(IF(A6&lt;TIME(9,45,0),B6,C6)=0,"",IF(A6&lt;TIME(9,45,0),B6,C6))</f>
+      <c r="E6" s="5" t="n">
+        <f aca="false">IF(IF(A6&lt;0.40625,B6,C6)=0,"",IF(A6&lt;0.40625,B6,C6))</f>
         <v>48</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>0.385416666666667</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <f aca="false">IF(IF(A7&lt;TIME(9,45,0),B7,C7)=0,"",IF(A7&lt;TIME(9,45,0),B7,C7))</f>
+      <c r="E7" s="5" t="n">
+        <f aca="false">IF(IF(A7&lt;0.40625,B7,C7)=0,"",IF(A7&lt;0.40625,B7,C7))</f>
         <v>79</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <f aca="false">IF(IF(A8&lt;TIME(9,45,0),B8,C8)=0,"",IF(A8&lt;TIME(9,45,0),B8,C8))</f>
+      <c r="E8" s="5" t="n">
+        <f aca="false">IF(IF(A8&lt;0.40625,B8,C8)=0,"",IF(A8&lt;0.40625,B8,C8))</f>
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>0.40625</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <f aca="false">IF(IF(A9&lt;TIME(9,45,0),B9,C9)=0,"",IF(A9&lt;TIME(9,45,0),B9,C9))</f>
+      <c r="E9" s="5" t="n">
+        <f aca="false">IF(IF(A9&lt;0.40625,B9,C9)=0,"",IF(A9&lt;0.40625,B9,C9))</f>
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>0.416666666666667</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <f aca="false">IF(IF(A10&lt;TIME(9,45,0),B10,C10)=0,"",IF(A10&lt;TIME(9,45,0),B10,C10))</f>
+      <c r="E10" s="5" t="n">
+        <f aca="false">IF(IF(A10&lt;0.40625,B10,C10)=0,"",IF(A10&lt;0.40625,B10,C10))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>0.427083333333333</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <f aca="false">IF(IF(A11&lt;TIME(9,45,0),B11,C11)=0,"",IF(A11&lt;TIME(9,45,0),B11,C11))</f>
+      <c r="E11" s="5" t="n">
+        <f aca="false">IF(IF(A11&lt;0.40625,B11,C11)=0,"",IF(A11&lt;0.40625,B11,C11))</f>
         <v>89</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <f aca="false">IF(IF(A12&lt;TIME(9,45,0),B12,C12)=0,"",IF(A12&lt;TIME(9,45,0),B12,C12))</f>
+      <c r="E12" s="5" t="n">
+        <f aca="false">IF(IF(A12&lt;0.40625,B12,C12)=0,"",IF(A12&lt;0.40625,B12,C12))</f>
         <v>41</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
         <v>0.447916666666667</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <f aca="false">IF(IF(A13&lt;TIME(9,45,0),B13,C13)=0,"",IF(A13&lt;TIME(9,45,0),B13,C13))</f>
+      <c r="E13" s="5" t="n">
+        <f aca="false">IF(IF(A13&lt;0.40625,B13,C13)=0,"",IF(A13&lt;0.40625,B13,C13))</f>
         <v>36</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="3" t="str">
-        <f aca="false">IF(IF(A14&lt;TIME(9,45,0),B14,C14)=0,"",IF(A14&lt;TIME(9,45,0),B14,C14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <f aca="false">SUM(B2:B14)</f>
         <v>316</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <f aca="false">SUM(C2:C14)</f>
         <v>232</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="4" t="n">
+      <c r="D15" s="2"/>
+      <c r="E15" s="5" t="n">
         <f aca="false">SUM(E2:E14)</f>
         <v>548</v>
       </c>

--- a/outputs/45372.xlsx
+++ b/outputs/45372.xlsx
@@ -128,27 +128,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -408,7 +408,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>0.333333333333333</v>
       </c>
@@ -430,11 +430,10 @@
         <v>42</v>
       </c>
       <c r="E2" s="5" t="n">
-        <f aca="false">IF(IF(A2&lt;0.40625,B2,C2)=0,"",IF(A2&lt;0.40625,B2,C2))</f>
         <v>42</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>0.34375</v>
       </c>
@@ -442,11 +441,10 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
-        <f aca="false">IF(IF(A3&lt;0.40625,B3,C3)=0,"",IF(A3&lt;0.40625,B3,C3))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>0.354166666666667</v>
       </c>
@@ -454,11 +452,10 @@
         <v>45</v>
       </c>
       <c r="E4" s="5" t="n">
-        <f aca="false">IF(IF(A4&lt;0.40625,B4,C4)=0,"",IF(A4&lt;0.40625,B4,C4))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>0.364583333333333</v>
       </c>
@@ -466,11 +463,10 @@
         <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">IF(IF(A5&lt;0.40625,B5,C5)=0,"",IF(A5&lt;0.40625,B5,C5))</f>
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>0.375</v>
       </c>
@@ -478,11 +474,10 @@
         <v>48</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">IF(IF(A6&lt;0.40625,B6,C6)=0,"",IF(A6&lt;0.40625,B6,C6))</f>
         <v>48</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>0.385416666666667</v>
       </c>
@@ -490,11 +485,10 @@
         <v>79</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">IF(IF(A7&lt;0.40625,B7,C7)=0,"",IF(A7&lt;0.40625,B7,C7))</f>
         <v>79</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>0.395833333333333</v>
       </c>
@@ -502,11 +496,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">IF(IF(A8&lt;0.40625,B8,C8)=0,"",IF(A8&lt;0.40625,B8,C8))</f>
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>0.40625</v>
       </c>
@@ -514,11 +507,10 @@
         <v>21</v>
       </c>
       <c r="E9" s="5" t="n">
-        <f aca="false">IF(IF(A9&lt;0.40625,B9,C9)=0,"",IF(A9&lt;0.40625,B9,C9))</f>
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>0.416666666666667</v>
       </c>
@@ -526,11 +518,10 @@
         <v>45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <f aca="false">IF(IF(A10&lt;0.40625,B10,C10)=0,"",IF(A10&lt;0.40625,B10,C10))</f>
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>0.427083333333333</v>
       </c>
@@ -538,11 +529,10 @@
         <v>89</v>
       </c>
       <c r="E11" s="5" t="n">
-        <f aca="false">IF(IF(A11&lt;0.40625,B11,C11)=0,"",IF(A11&lt;0.40625,B11,C11))</f>
         <v>89</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>0.4375</v>
       </c>
@@ -550,11 +540,10 @@
         <v>41</v>
       </c>
       <c r="E12" s="5" t="n">
-        <f aca="false">IF(IF(A12&lt;0.40625,B12,C12)=0,"",IF(A12&lt;0.40625,B12,C12))</f>
         <v>41</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>0.447916666666667</v>
       </c>
@@ -562,14 +551,13 @@
         <v>36</v>
       </c>
       <c r="E13" s="5" t="n">
-        <f aca="false">IF(IF(A13&lt;0.40625,B13,C13)=0,"",IF(A13&lt;0.40625,B13,C13))</f>
         <v>36</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
